--- a/artfynd/A 54095-2025 artfynd.xlsx
+++ b/artfynd/A 54095-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AZ46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95981699</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104442989</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887711</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1111,6 +1131,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887709</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1218,6 +1243,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887694</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1325,6 +1355,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887700</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1432,6 +1467,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887701</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1539,6 +1579,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887705</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1646,6 +1691,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887706</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1753,6 +1803,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887712</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1860,6 +1915,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887715</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1961,6 +2021,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95981698</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2062,6 +2127,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95981681</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2176,6 +2246,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89046681</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2283,6 +2358,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887693</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2390,6 +2470,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887699</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2497,6 +2582,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887720</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2604,6 +2694,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887722</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2711,6 +2806,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887725</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2812,6 +2912,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95981682</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2919,6 +3024,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887696</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3026,6 +3136,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887697</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3133,6 +3248,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887708</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3240,6 +3360,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887713</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3347,6 +3472,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887721</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3448,6 +3578,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95981693</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3562,6 +3697,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89046686</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3682,6 +3822,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887692</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3802,6 +3947,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887703</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3922,6 +4072,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887710</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4042,6 +4197,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887718</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4162,6 +4322,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887723</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4281,6 +4446,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887707</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4382,6 +4552,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95981676</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4483,6 +4658,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95981692</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4584,6 +4764,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95981696</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4690,6 +4875,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104442990</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4791,6 +4981,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95981683</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4902,6 +5097,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104442988</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5009,6 +5209,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887695</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5116,6 +5321,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887698</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5223,6 +5433,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887704</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5330,6 +5545,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887714</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5437,6 +5657,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887716</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5544,8 +5769,60 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887724</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>